--- a/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
+++ b/InputData/elec/SoFCtMbCtPR/Shr of Fwd Costs that Must be Covered to be Prevent Retirement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\elec\SoFCtMbCtPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoFCtMbCtPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD62E26-F9D9-4031-99DB-E69C50D6FF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC69FDE-83D8-45D5-8861-B60A41C383AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10350" yWindow="795" windowWidth="19110" windowHeight="16425" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="3090" yWindow="4410" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -616,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
